--- a/05 Others/2026.1 Avaliação Projetos/Turma Python IoT - ARA0058 Turma 3002 PRESENCIAL Wyden UniRuy 2026_1.xlsx
+++ b/05 Others/2026.1 Avaliação Projetos/Turma Python IoT - ARA0058 Turma 3002 PRESENCIAL Wyden UniRuy 2026_1.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YduqsArea1\Avaliações Yduqs 2022_2 BDQ 2023_1 2024_2\2026.1 Avaliação Projetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E8264A5-08A9-49F7-AE32-5E5BCA922AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22121270-E5B2-4484-AAD3-B5F3B01AABA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DD6ED3E7-57DF-4A52-9E4C-63B0F7661B3D}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$H$26</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="34">
-  <si>
-    <t>-</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="50">
   <si>
     <t>Falta</t>
   </si>
@@ -138,13 +138,64 @@
   </si>
   <si>
     <t>PROJ</t>
+  </si>
+  <si>
+    <t>EQ</t>
+  </si>
+  <si>
+    <t>https://github.com/adersan/ecosense-iot</t>
+  </si>
+  <si>
+    <t>https://github.com/AndrezaLma/-1o-Semin-rio-Sistema-Repasse-Medico-UniRuy-Wyden - seria reprovada - não procede aluna EAD</t>
+  </si>
+  <si>
+    <t>https://github.com/GabriellaMizrach/Seguranca_em_IoT_Validacao_Fisica_de_Gemeos_Digitais</t>
+  </si>
+  <si>
+    <t>https://github.com/GuilhermeMiguel-DEV/ESP_SPC</t>
+  </si>
+  <si>
+    <t>https://github.com/MateusTrindade/projeto-iot-tinkercad</t>
+  </si>
+  <si>
+    <t>https://github.com/JoaoVictorCarvalho-DEV/spc</t>
+  </si>
+  <si>
+    <t>https://github.com/PnpmGK/SISTEMA-AUTOMATIZADO-DE-SINALIZA-O-INDUSTRIAL-COM-ARDUINO-UNO</t>
+  </si>
+  <si>
+    <t>https://github.com/LeviDevGit/sistema-logistica-arduino</t>
+  </si>
+  <si>
+    <t>https://github.com/lu-sntss/esp_wheather_sensor_monitoring</t>
+  </si>
+  <si>
+    <t>https://github.com/Tavaresreistk/Projeto-Arduino-Iot-4.0/tree/main</t>
+  </si>
+  <si>
+    <t>Link tinkercad não disponível</t>
+  </si>
+  <si>
+    <t>https://github.com/MajuGoes/SMARTGAS_Cloud_IOT</t>
+  </si>
+  <si>
+    <t>https://github.com/Thallycs/Sinaleira-Inteligente-IoT</t>
+  </si>
+  <si>
+    <t>https://github.com/tiagogc15/Irriga-o-automatica</t>
+  </si>
+  <si>
+    <t>Link tinkercad não disponível; readme</t>
+  </si>
+  <si>
+    <t>não GitHub</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,8 +222,22 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -185,8 +250,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -377,11 +448,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -404,9 +487,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -419,11 +499,39 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -756,467 +864,701 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0212B8F-44EC-4B38-84EB-21D2846DA7CB}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultColWidth="84.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="65.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="7">
+        <v>17</v>
+      </c>
+      <c r="C2" s="7">
+        <v>1</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="7">
+        <v>10</v>
+      </c>
+      <c r="F2" s="7">
+        <f>E2</f>
+        <v>10</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="C3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
         <v>6</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F3" s="5">
+        <f t="shared" ref="F3:F26" si="0">E3</f>
+        <v>6</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="C4" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>10</v>
+      </c>
+      <c r="F4" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="5">
+        <v>12</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="E5" s="5">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>10</v>
+      </c>
+      <c r="F6" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="5">
+        <v>11</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="E7" s="5">
+        <v>9</v>
+      </c>
+      <c r="F7" s="5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="5">
+        <v>14</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="E8" s="5">
+        <v>10</v>
+      </c>
+      <c r="F8" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="5">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>10</v>
+      </c>
+      <c r="F9" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="5">
+        <v>12</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="E10" s="5">
+        <v>10</v>
+      </c>
+      <c r="F10" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="5">
+        <v>6</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="E11" s="5">
+        <v>8</v>
+      </c>
+      <c r="F11" s="5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="5">
+        <v>6</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="E12" s="5">
+        <v>8</v>
+      </c>
+      <c r="F12" s="5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="5">
+        <v>16</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>9.5</v>
+      </c>
+      <c r="F13" s="5">
+        <f t="shared" si="0"/>
+        <v>9.5</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="5">
+        <v>12</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="E14" s="5">
+        <v>10</v>
+      </c>
+      <c r="F14" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="5">
+        <v>4</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="E15" s="5">
+        <v>7.5</v>
+      </c>
+      <c r="F15" s="5">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="5">
+        <v>18</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E16" s="5">
+        <v>10</v>
+      </c>
+      <c r="F16" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="5">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>10</v>
+      </c>
+      <c r="F17" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="5">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5">
+        <v>9</v>
+      </c>
+      <c r="F18" s="5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="5">
+        <v>5</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="E19" s="5">
+        <v>10</v>
+      </c>
+      <c r="F19" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="5">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="E20" s="5">
+        <v>8</v>
+      </c>
+      <c r="F20" s="5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="5">
+        <v>9</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5">
+        <v>10</v>
+      </c>
+      <c r="F21" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="20">
+        <v>19</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E22" s="20">
+        <v>0</v>
+      </c>
+      <c r="F22" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="5">
+        <v>9</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="E23" s="5">
+        <v>10</v>
+      </c>
+      <c r="F23" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="5">
+        <v>9</v>
+      </c>
+      <c r="C24" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="E24" s="5">
+        <v>10</v>
+      </c>
+      <c r="F24" s="5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="5">
+        <v>13</v>
+      </c>
+      <c r="C25" s="5">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="E25" s="5">
         <v>7</v>
       </c>
-      <c r="B2" s="7">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+      <c r="F25" s="5">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="11">
         <v>8</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="C5" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="C7" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="5">
+      <c r="C26" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="11">
         <v>0.9</v>
       </c>
-      <c r="C11" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="5">
-        <v>1</v>
-      </c>
-      <c r="C14" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="C15" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="C19" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="C20" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="C23" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="C24" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="5">
-        <v>1</v>
-      </c>
-      <c r="C25" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
+      <c r="E26" s="11">
+        <v>10</v>
+      </c>
+      <c r="F26" s="11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" s="12">
-        <v>0.9</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E26" s="12"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>32</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H26" xr:uid="{D0212B8F-44EC-4B38-84EB-21D2846DA7CB}"/>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{93E3E646-A1D1-4D67-A10B-3AFCE6A35391}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{E81CE3A8-A500-4976-A592-6F661C798EEB}"/>
+    <hyperlink ref="G10" r:id="rId3" xr:uid="{AC2AB48B-7409-4DE2-A73A-6A1940741B0C}"/>
+    <hyperlink ref="G14" r:id="rId4" xr:uid="{7FC87E2E-79B4-4640-BBAF-75B719A064AB}"/>
+    <hyperlink ref="G5" r:id="rId5" xr:uid="{FBC6302F-F2FC-4C4F-ABC1-891741B1328C}"/>
+    <hyperlink ref="G11" r:id="rId6" xr:uid="{A2BDA632-F847-42C3-923C-4D4D5D67CF4A}"/>
+    <hyperlink ref="G12" r:id="rId7" xr:uid="{30F63C1C-6064-4B2F-AE90-4BB59A4A2A22}"/>
+    <hyperlink ref="G20" r:id="rId8" xr:uid="{3CA7FE58-FC4D-4B19-BD45-6E8746597518}"/>
+    <hyperlink ref="G15" r:id="rId9" xr:uid="{62701595-A4CA-4027-831D-F19294B479E7}"/>
+    <hyperlink ref="G16" r:id="rId10" xr:uid="{B37AEF7A-A828-48CD-8709-952FFDF68FA8}"/>
+    <hyperlink ref="G17" r:id="rId11" xr:uid="{AC97EAB7-6CF9-433E-806C-E1475268F2AE}"/>
+    <hyperlink ref="G9" r:id="rId12" xr:uid="{BFE7120C-FEF4-43CF-9BFC-6895B077AD46}"/>
+    <hyperlink ref="G26" r:id="rId13" xr:uid="{29D0C2CA-CE8B-4071-A050-D7A7F611D6FC}"/>
+    <hyperlink ref="G18" r:id="rId14" xr:uid="{7ABFE015-6564-4577-9729-A7143F2A19D5}"/>
+    <hyperlink ref="G19" r:id="rId15" xr:uid="{D6DF2D76-0D0F-457A-BE0F-342121210554}"/>
+    <hyperlink ref="G4" r:id="rId16" xr:uid="{47B1E8D8-D556-47C9-9719-BE9446B6DBFA}"/>
+    <hyperlink ref="G6" r:id="rId17" xr:uid="{C3F8C7F3-3D91-4646-8B99-A11BBA4C4C2E}"/>
+    <hyperlink ref="G21" r:id="rId18" xr:uid="{0149BD13-B6EC-4AF5-AEC6-85FE04D55BAD}"/>
+    <hyperlink ref="G23" r:id="rId19" xr:uid="{2AA27496-1E3B-4FF5-885E-30634225AE24}"/>
+    <hyperlink ref="G24" r:id="rId20" xr:uid="{F4305D01-78BB-4A84-B837-B330EEFADAEC}"/>
+    <hyperlink ref="G25" r:id="rId21" xr:uid="{1719D638-F74A-4381-8CD9-19971047F31F}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId22"/>
 </worksheet>
 </file>
--- a/05 Others/2026.1 Avaliação Projetos/Turma Python IoT - ARA0058 Turma 3002 PRESENCIAL Wyden UniRuy 2026_1.xlsx
+++ b/05 Others/2026.1 Avaliação Projetos/Turma Python IoT - ARA0058 Turma 3002 PRESENCIAL Wyden UniRuy 2026_1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YduqsArea1\Avaliações Yduqs 2022_2 BDQ 2023_1 2024_2\2026.1 Avaliação Projetos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YduqsArea1\Avaliações Yduqs 2022_2 BDQ 2023_1 2024_2\2026.1 Avaliação Projetos\ok\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22121270-E5B2-4484-AAD3-B5F3B01AABA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31763F0-E799-4477-B23F-70A397810092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DD6ED3E7-57DF-4A52-9E4C-63B0F7661B3D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="52">
   <si>
     <t>Falta</t>
   </si>
@@ -188,14 +188,20 @@
     <t>Link tinkercad não disponível; readme</t>
   </si>
   <si>
-    <t>não GitHub</t>
+    <t>não GitHub/SAVA</t>
+  </si>
+  <si>
+    <t>não apresentou</t>
+  </si>
+  <si>
+    <t>apresentou</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,8 +242,14 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -253,6 +265,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +482,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -520,13 +538,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1047,7 +1068,9 @@
       <c r="G7" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="1"/>
+      <c r="H7" s="22" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
@@ -1197,7 +1220,9 @@
       <c r="G13" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="H13" s="1"/>
+      <c r="H13" s="22" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
@@ -1402,29 +1427,31 @@
       <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="21">
         <v>19</v>
       </c>
-      <c r="C22" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="E22" s="20">
-        <v>0</v>
-      </c>
-      <c r="F22" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="21" t="s">
+      <c r="C22" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E22" s="21">
+        <v>0</v>
+      </c>
+      <c r="F22" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="H22" s="1"/>
+      <c r="H22" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
